--- a/tests/data/synthetic-layouts/pdf-source.xlsx
+++ b/tests/data/synthetic-layouts/pdf-source.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="F21" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="F57" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="F21" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -7915,7 +7915,7 @@
       </c>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="F57" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -9037,7 +9037,7 @@
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10159,7 +10159,7 @@
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10907,7 +10907,7 @@
       </c>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
